--- a/results/Int Task Remove ACC -0.9/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_8_permute.xlsx
@@ -440,27 +440,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6500654397727232</v>
+        <v>0.6153254712536167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6509295937847921</v>
+        <v>0.5925578400337843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6275667223922687</v>
+        <v>0.606807830435951</v>
       </c>
     </row>
     <row r="5">
@@ -470,857 +470,857 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6264607029802145</v>
+        <v>0.601675956205959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6261052341347815</v>
+        <v>0.5991897683606552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.639524401182453</v>
+        <v>0.6018344077089797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6144539879870028</v>
+        <v>0.6070038007419998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5914486795126395</v>
+        <v>0.6055819253602678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5897516080733484</v>
+        <v>0.5890448585279366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5948053035881936</v>
+        <v>0.5875051915553027</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5558946402208549</v>
+        <v>0.5822513375889544</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5679722046746684</v>
+        <v>0.5907033641278362</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5680899962655703</v>
+        <v>0.6045884623572977</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5682088348928358</v>
+        <v>0.5995743797182076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5676532075958998</v>
+        <v>0.6073884120995522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5679294506898225</v>
+        <v>0.6022586319422873</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5741256373833863</v>
+        <v>0.6165033871626362</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5742027690621695</v>
+        <v>0.608570516154026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5657914024354066</v>
+        <v>0.6263313939893133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5657914024354066</v>
+        <v>0.6270016717680604</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.558443301235852</v>
+        <v>0.6294492937739729</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.558443301235852</v>
+        <v>0.6247864918348613</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5475905948213582</v>
+        <v>0.5866618037644447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5322314438980466</v>
+        <v>0.5935314093458466</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5325076869919693</v>
+        <v>0.5970433438153306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.527771941519529</v>
+        <v>0.5970433438153306</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.504801010739103</v>
+        <v>0.5826776558949892</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4927641061974082</v>
+        <v>0.5533625572816143</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4712452403471973</v>
+        <v>0.5271016637407817</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4711429797956883</v>
+        <v>0.5114329390659738</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4596981743175941</v>
+        <v>0.4733082509955571</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4596981743175941</v>
+        <v>0.4781242692558713</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4596981743175941</v>
+        <v>0.4773341058134949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4577634256237719</v>
+        <v>0.4827807889768012</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4719664738956384</v>
+        <v>0.4778740275649773</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4337082886888661</v>
+        <v>0.4404936078430004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4376153048795385</v>
+        <v>0.4468377756759492</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4443254119215561</v>
+        <v>0.4297419404375914</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4550154786875748</v>
+        <v>0.4262685718074989</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4513440456787065</v>
+        <v>0.4275319956862102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.454464039536093</v>
+        <v>0.4599150853509142</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.457070113045026</v>
+        <v>0.4694658020473051</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4479999860395152</v>
+        <v>0.4691113802382357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4339449189070337</v>
+        <v>0.4439325987791556</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4857828167372253</v>
+        <v>0.4433008868398</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4853085092645267</v>
+        <v>0.4414036569490059</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4615734164447531</v>
+        <v>0.4201058902775693</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4610167421114535</v>
+        <v>0.4620313203477557</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4329045137737634</v>
+        <v>0.4717790543865588</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4295478896982092</v>
+        <v>0.4620426632416944</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4287587732921965</v>
+        <v>0.468286839101922</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4304568917678511</v>
+        <v>0.4704487946866395</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4155741423899652</v>
+        <v>0.455572327526935</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4374671492340929</v>
+        <v>0.4429422768852762</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4331671453949595</v>
+        <v>0.4615974982811153</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4675715387595412</v>
+        <v>0.4537428059876519</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.437216035012896</v>
+        <v>0.5033990290482788</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4458889862244916</v>
+        <v>0.5033990290482788</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4619068975265511</v>
+        <v>0.4347434586403186</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4260984283984183</v>
+        <v>0.4358807146372193</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4632767701022257</v>
+        <v>0.4284586228679722</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4632767701022257</v>
+        <v>0.4532349933513191</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4850437835706034</v>
+        <v>0.4525912404937824</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4899796874945467</v>
+        <v>0.4542497460936818</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4634905400264551</v>
+        <v>0.4554339442208828</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4621875032719887</v>
+        <v>0.4928998719125515</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4390924986824792</v>
+        <v>0.493847439821585</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4017747266362561</v>
+        <v>0.4869329861826102</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3862581712462874</v>
+        <v>0.479400432077006</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3850322661706041</v>
+        <v>0.4970227521001804</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3677404606261976</v>
+        <v>0.4970227521001804</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3611074852629632</v>
+        <v>0.4857405862705612</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4326001752040848</v>
+        <v>0.4887031756612907</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4550988925845394</v>
+        <v>0.4887031756612907</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4735290011622104</v>
+        <v>0.4856550783008693</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4771868226983523</v>
+        <v>0.4862836491311343</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4940898287397522</v>
+        <v>0.4815437155132398</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4827711911434684</v>
+        <v>0.4990868097849038</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4991068779818723</v>
+        <v>0.4994016187182181</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4978841140152798</v>
+        <v>0.4994016187182181</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4978841140152798</v>
+        <v>0.4960481357517547</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4933881398700977</v>
+        <v>0.4931262062731439</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5085595222722086</v>
+        <v>0.4979443186061852</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5070980340147213</v>
+        <v>0.4982205617001078</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5252728402257411</v>
+        <v>0.4983383532910098</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.526605019492327</v>
+        <v>0.4983383532910098</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5106549910478391</v>
+        <v>0.500866248084796</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5250301022954528</v>
+        <v>0.4999979059272729</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4977760947637712</v>
+        <v>0.5008672951211596</v>
       </c>
     </row>
   </sheetData>
